--- a/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-organization.xlsx
+++ b/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T08:09:55+00:00</t>
+    <t>2026-08-20T16:34:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-organization.xlsx
+++ b/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T16:34:37+00:00</t>
+    <t>2026-08-21T09:28:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-organization.xlsx
+++ b/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T09:28:33+00:00</t>
+    <t>2026-08-21T09:39:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-organization.xlsx
+++ b/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T09:39:43+00:00</t>
+    <t>2026-08-21T14:30:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-organization.xlsx
+++ b/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T14:30:36+00:00</t>
+    <t>2026-08-21T16:03:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-organization.xlsx
+++ b/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T16:03:39+00:00</t>
+    <t>2026-08-26T13:04:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -716,6 +716,12 @@
   </si>
   <si>
     <t>The date range that this organization should be considered available.</t>
+  </si>
+  <si>
+    <t>dateFermeture (uniquement)</t>
+  </si>
+  <si>
+    <t>dateOuverture et dateFermeture</t>
   </si>
   <si>
     <t>Organization.extension:usePeriod.id</t>
@@ -1353,12 +1359,6 @@
   </si>
   <si>
     <t>dateOuverture (EG) + dateFermeture (EJ + EG)</t>
-  </si>
-  <si>
-    <t>dateFermeture (uniquement)</t>
-  </si>
-  <si>
-    <t>dateOuverture et dateFermeture</t>
   </si>
   <si>
     <t>Organization.extension:ror-meta-comment</t>
@@ -7407,10 +7407,10 @@
         <v>123</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>80</v>
+        <v>225</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>80</v>
+        <v>226</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>80</v>
@@ -7433,10 +7433,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -7557,10 +7557,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -7681,10 +7681,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -7710,13 +7710,13 @@
         <v>137</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>80</v>
@@ -7766,7 +7766,7 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>92</v>
@@ -7807,10 +7807,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -7833,13 +7833,13 @@
         <v>80</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -7890,7 +7890,7 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -7899,7 +7899,7 @@
         <v>92</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>105</v>
@@ -7931,10 +7931,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -8055,10 +8055,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -8181,10 +8181,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -8207,16 +8207,16 @@
         <v>93</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -8266,7 +8266,7 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -8275,7 +8275,7 @@
         <v>92</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>105</v>
@@ -8287,16 +8287,16 @@
         <v>80</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>80</v>
@@ -8307,10 +8307,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -8333,23 +8333,23 @@
         <v>93</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q30" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="R30" t="s" s="2">
         <v>80</v>
@@ -8394,7 +8394,7 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -8403,7 +8403,7 @@
         <v>92</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>105</v>
@@ -8415,16 +8415,16 @@
         <v>80</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AQ30" t="s" s="2">
         <v>80</v>
@@ -8435,13 +8435,13 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>206</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>80</v>
@@ -8463,16 +8463,16 @@
         <v>80</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -8563,13 +8563,13 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>206</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D32" t="s" s="2">
         <v>80</v>
@@ -8591,16 +8591,16 @@
         <v>80</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -8691,13 +8691,13 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>206</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D33" t="s" s="2">
         <v>80</v>
@@ -8719,13 +8719,13 @@
         <v>80</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -8817,13 +8817,13 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>206</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>80</v>
@@ -8845,13 +8845,13 @@
         <v>80</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -8943,13 +8943,13 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>206</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>80</v>
@@ -8971,13 +8971,13 @@
         <v>80</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -9069,13 +9069,13 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>206</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>80</v>
@@ -9097,13 +9097,13 @@
         <v>80</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -9195,13 +9195,13 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>206</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D37" t="s" s="2">
         <v>80</v>
@@ -9223,13 +9223,13 @@
         <v>80</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -9301,7 +9301,7 @@
         <v>80</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>80</v>
@@ -9321,13 +9321,13 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>206</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D38" t="s" s="2">
         <v>80</v>
@@ -9349,13 +9349,13 @@
         <v>80</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -9430,7 +9430,7 @@
         <v>80</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>80</v>
@@ -9447,13 +9447,13 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>206</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>80</v>
@@ -9475,13 +9475,13 @@
         <v>80</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -9553,10 +9553,10 @@
         <v>80</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>80</v>
@@ -9573,13 +9573,13 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>206</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>80</v>
@@ -9601,13 +9601,13 @@
         <v>80</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -9682,7 +9682,7 @@
         <v>80</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>80</v>
@@ -9699,13 +9699,13 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>206</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D41" t="s" s="2">
         <v>80</v>
@@ -9727,13 +9727,13 @@
         <v>80</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -9808,7 +9808,7 @@
         <v>80</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>80</v>
@@ -9825,13 +9825,13 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>206</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D42" t="s" s="2">
         <v>80</v>
@@ -9853,13 +9853,13 @@
         <v>80</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -9928,7 +9928,7 @@
         <v>80</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>80</v>
@@ -9951,13 +9951,13 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>206</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D43" t="s" s="2">
         <v>80</v>
@@ -9979,13 +9979,13 @@
         <v>80</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -10054,7 +10054,7 @@
         <v>80</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>80</v>
@@ -10077,10 +10077,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -10201,10 +10201,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>82</v>
@@ -10325,13 +10325,13 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D46" t="s" s="2">
         <v>80</v>
@@ -10451,10 +10451,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -10575,10 +10575,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -10699,10 +10699,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -10728,13 +10728,13 @@
         <v>137</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="S49" t="s" s="2">
         <v>80</v>
@@ -10784,7 +10784,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>92</v>
@@ -10825,10 +10825,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -10851,13 +10851,13 @@
         <v>80</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -10869,7 +10869,7 @@
         <v>80</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="T50" t="s" s="2">
         <v>80</v>
@@ -10888,7 +10888,7 @@
       </c>
       <c r="Y50" s="2"/>
       <c r="Z50" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>80</v>
@@ -10906,7 +10906,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -10947,13 +10947,13 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>80</v>
@@ -11073,10 +11073,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -11197,10 +11197,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -11321,10 +11321,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -11350,13 +11350,13 @@
         <v>137</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="Q54" s="2"/>
       <c r="R54" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="S54" t="s" s="2">
         <v>80</v>
@@ -11406,7 +11406,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>92</v>
@@ -11447,10 +11447,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -11473,13 +11473,13 @@
         <v>80</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -11510,7 +11510,7 @@
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>80</v>
@@ -11528,7 +11528,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -11569,10 +11569,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -11598,13 +11598,13 @@
         <v>137</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="Q56" s="2"/>
       <c r="R56" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="S56" t="s" s="2">
         <v>80</v>
@@ -11654,7 +11654,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>92</v>
@@ -11695,10 +11695,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -11721,13 +11721,13 @@
         <v>80</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -11778,7 +11778,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -11819,13 +11819,13 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B58" t="s" s="2">
         <v>206</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D58" t="s" s="2">
         <v>80</v>
@@ -11847,13 +11847,13 @@
         <v>80</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -11922,7 +11922,7 @@
         <v>80</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>80</v>
@@ -11945,13 +11945,13 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B59" t="s" s="2">
         <v>206</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D59" t="s" s="2">
         <v>80</v>
@@ -11973,13 +11973,13 @@
         <v>80</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -12048,7 +12048,7 @@
         <v>80</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>80</v>
@@ -12071,13 +12071,13 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>206</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D60" t="s" s="2">
         <v>80</v>
@@ -12099,13 +12099,13 @@
         <v>80</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -12174,7 +12174,7 @@
         <v>80</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>80</v>
@@ -12197,13 +12197,13 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B61" t="s" s="2">
         <v>206</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D61" t="s" s="2">
         <v>80</v>
@@ -12225,13 +12225,13 @@
         <v>80</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -12300,7 +12300,7 @@
         <v>80</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>80</v>
@@ -12323,13 +12323,13 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B62" t="s" s="2">
         <v>206</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D62" t="s" s="2">
         <v>80</v>
@@ -12351,13 +12351,13 @@
         <v>80</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -12426,7 +12426,7 @@
         <v>80</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>80</v>
@@ -12449,13 +12449,13 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B63" t="s" s="2">
         <v>206</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D63" t="s" s="2">
         <v>80</v>
@@ -12477,13 +12477,13 @@
         <v>80</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -12552,7 +12552,7 @@
         <v>80</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>80</v>
@@ -12575,13 +12575,13 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B64" t="s" s="2">
         <v>206</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D64" t="s" s="2">
         <v>80</v>
@@ -12603,13 +12603,13 @@
         <v>80</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -12678,7 +12678,7 @@
         <v>80</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>80</v>
@@ -12701,13 +12701,13 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B65" t="s" s="2">
         <v>206</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D65" t="s" s="2">
         <v>80</v>
@@ -12729,13 +12729,13 @@
         <v>80</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -12801,7 +12801,7 @@
         <v>123</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>80</v>
@@ -12827,13 +12827,13 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B66" t="s" s="2">
         <v>206</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D66" t="s" s="2">
         <v>80</v>
@@ -12855,13 +12855,13 @@
         <v>80</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -12927,10 +12927,10 @@
         <v>123</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>80</v>
@@ -12953,13 +12953,13 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>206</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D67" t="s" s="2">
         <v>80</v>
@@ -12981,10 +12981,10 @@
         <v>80</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="M67" t="s" s="2">
         <v>224</v>
@@ -13053,10 +13053,10 @@
         <v>123</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>426</v>
+        <v>80</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>427</v>
+        <v>80</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>80</v>
@@ -14367,7 +14367,7 @@
         <v>93</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L78" t="s" s="2">
         <v>491</v>
@@ -14747,7 +14747,7 @@
         <v>93</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="L81" t="s" s="2">
         <v>523</v>
@@ -15501,7 +15501,7 @@
         <v>93</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L87" t="s" s="2">
         <v>491</v>
@@ -15881,7 +15881,7 @@
         <v>93</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="L90" t="s" s="2">
         <v>523</v>
@@ -16637,7 +16637,7 @@
         <v>93</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L96" t="s" s="2">
         <v>491</v>
@@ -17017,7 +17017,7 @@
         <v>93</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="L99" t="s" s="2">
         <v>523</v>
@@ -17771,7 +17771,7 @@
         <v>93</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L105" t="s" s="2">
         <v>491</v>
@@ -19541,7 +19541,7 @@
         <v>93</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="L119" t="s" s="2">
         <v>523</v>
@@ -20295,7 +20295,7 @@
         <v>93</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L125" t="s" s="2">
         <v>491</v>
@@ -20675,7 +20675,7 @@
         <v>93</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="L128" t="s" s="2">
         <v>523</v>
@@ -21431,7 +21431,7 @@
         <v>93</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L134" t="s" s="2">
         <v>491</v>
@@ -21813,7 +21813,7 @@
         <v>93</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="L137" t="s" s="2">
         <v>523</v>
@@ -22195,7 +22195,7 @@
         <v>93</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L140" t="s" s="2">
         <v>704</v>
@@ -22321,7 +22321,7 @@
         <v>93</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L141" t="s" s="2">
         <v>714</v>
@@ -23072,13 +23072,13 @@
         <v>137</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
@@ -23128,7 +23128,7 @@
         <v>80</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>92</v>
@@ -23198,10 +23198,10 @@
         <v>182</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
@@ -23250,7 +23250,7 @@
         <v>80</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>81</v>
@@ -24459,7 +24459,7 @@
         <v>93</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L158" t="s" s="2">
         <v>756</v>
@@ -25210,13 +25210,13 @@
         <v>137</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O164" s="2"/>
       <c r="P164" t="s" s="2">
@@ -25266,7 +25266,7 @@
         <v>80</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>92</v>
@@ -25336,10 +25336,10 @@
         <v>182</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="N165" s="2"/>
       <c r="O165" s="2"/>
@@ -25388,7 +25388,7 @@
         <v>80</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>81</v>
@@ -26597,7 +26597,7 @@
         <v>93</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L175" t="s" s="2">
         <v>777</v>
@@ -28115,7 +28115,7 @@
         <v>93</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L187" t="s" s="2">
         <v>793</v>
@@ -28866,13 +28866,13 @@
         <v>137</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N193" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O193" s="2"/>
       <c r="P193" t="s" s="2">
@@ -28922,7 +28922,7 @@
         <v>80</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>92</v>
@@ -28992,10 +28992,10 @@
         <v>182</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="N194" s="2"/>
       <c r="O194" s="2"/>
@@ -29044,7 +29044,7 @@
         <v>80</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>81</v>
@@ -29369,7 +29369,7 @@
         <v>93</v>
       </c>
       <c r="K197" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L197" t="s" s="2">
         <v>809</v>
@@ -30120,13 +30120,13 @@
         <v>137</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N203" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O203" s="2"/>
       <c r="P203" t="s" s="2">
@@ -30176,7 +30176,7 @@
         <v>80</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>92</v>
@@ -30246,10 +30246,10 @@
         <v>182</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="N204" s="2"/>
       <c r="O204" s="2"/>
@@ -30298,7 +30298,7 @@
         <v>80</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>81</v>
@@ -30623,7 +30623,7 @@
         <v>93</v>
       </c>
       <c r="K207" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L207" t="s" s="2">
         <v>824</v>
@@ -31374,13 +31374,13 @@
         <v>137</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N213" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O213" s="2"/>
       <c r="P213" t="s" s="2">
@@ -31430,7 +31430,7 @@
         <v>80</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>92</v>
@@ -31500,10 +31500,10 @@
         <v>182</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="N214" s="2"/>
       <c r="O214" s="2"/>
@@ -31552,7 +31552,7 @@
         <v>80</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>81</v>
@@ -31877,7 +31877,7 @@
         <v>93</v>
       </c>
       <c r="K217" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L217" t="s" s="2">
         <v>838</v>
@@ -32079,7 +32079,7 @@
         <v>105</v>
       </c>
       <c r="AK218" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AL218" t="s" s="2">
         <v>846</v>
@@ -33767,7 +33767,7 @@
         <v>93</v>
       </c>
       <c r="K232" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="L232" t="s" s="2">
         <v>930</v>
@@ -34646,13 +34646,13 @@
         <v>137</v>
       </c>
       <c r="L239" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="M239" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N239" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O239" s="2"/>
       <c r="P239" t="s" s="2">
@@ -34702,7 +34702,7 @@
         <v>80</v>
       </c>
       <c r="AF239" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG239" t="s" s="2">
         <v>92</v>
@@ -34772,10 +34772,10 @@
         <v>154</v>
       </c>
       <c r="L240" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M240" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="N240" s="2"/>
       <c r="O240" s="2"/>
@@ -34824,7 +34824,7 @@
         <v>80</v>
       </c>
       <c r="AF240" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AG240" t="s" s="2">
         <v>81</v>
@@ -35644,13 +35644,13 @@
         <v>137</v>
       </c>
       <c r="L247" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="M247" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N247" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O247" s="2"/>
       <c r="P247" t="s" s="2">
@@ -35700,7 +35700,7 @@
         <v>80</v>
       </c>
       <c r="AF247" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG247" t="s" s="2">
         <v>92</v>
@@ -35767,13 +35767,13 @@
         <v>80</v>
       </c>
       <c r="K248" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L248" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M248" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="N248" s="2"/>
       <c r="O248" s="2"/>
@@ -35822,7 +35822,7 @@
         <v>80</v>
       </c>
       <c r="AF248" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AG248" t="s" s="2">
         <v>81</v>
@@ -36266,13 +36266,13 @@
         <v>137</v>
       </c>
       <c r="L252" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="M252" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N252" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O252" s="2"/>
       <c r="P252" t="s" s="2">
@@ -36322,7 +36322,7 @@
         <v>80</v>
       </c>
       <c r="AF252" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG252" t="s" s="2">
         <v>92</v>
@@ -36392,10 +36392,10 @@
         <v>108</v>
       </c>
       <c r="L253" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M253" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="N253" s="2"/>
       <c r="O253" s="2"/>
@@ -36446,7 +36446,7 @@
         <v>80</v>
       </c>
       <c r="AF253" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AG253" t="s" s="2">
         <v>81</v>
@@ -36890,13 +36890,13 @@
         <v>137</v>
       </c>
       <c r="L257" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="M257" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N257" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O257" s="2"/>
       <c r="P257" t="s" s="2">
@@ -36946,7 +36946,7 @@
         <v>80</v>
       </c>
       <c r="AF257" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG257" t="s" s="2">
         <v>92</v>
@@ -37016,10 +37016,10 @@
         <v>108</v>
       </c>
       <c r="L258" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M258" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="N258" s="2"/>
       <c r="O258" s="2"/>
@@ -37070,7 +37070,7 @@
         <v>80</v>
       </c>
       <c r="AF258" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AG258" t="s" s="2">
         <v>81</v>
@@ -37514,13 +37514,13 @@
         <v>137</v>
       </c>
       <c r="L262" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="M262" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N262" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O262" s="2"/>
       <c r="P262" t="s" s="2">
@@ -37570,7 +37570,7 @@
         <v>80</v>
       </c>
       <c r="AF262" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG262" t="s" s="2">
         <v>92</v>
@@ -37640,10 +37640,10 @@
         <v>108</v>
       </c>
       <c r="L263" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M263" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="N263" s="2"/>
       <c r="O263" s="2"/>
@@ -37694,7 +37694,7 @@
         <v>80</v>
       </c>
       <c r="AF263" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AG263" t="s" s="2">
         <v>81</v>
@@ -38138,13 +38138,13 @@
         <v>137</v>
       </c>
       <c r="L267" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="M267" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N267" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O267" s="2"/>
       <c r="P267" t="s" s="2">
@@ -38194,7 +38194,7 @@
         <v>80</v>
       </c>
       <c r="AF267" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG267" t="s" s="2">
         <v>92</v>
@@ -38264,10 +38264,10 @@
         <v>635</v>
       </c>
       <c r="L268" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M268" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="N268" s="2"/>
       <c r="O268" s="2"/>
@@ -38318,7 +38318,7 @@
         <v>80</v>
       </c>
       <c r="AF268" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AG268" t="s" s="2">
         <v>81</v>
@@ -38388,13 +38388,13 @@
         <v>137</v>
       </c>
       <c r="L269" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="M269" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N269" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O269" s="2"/>
       <c r="P269" t="s" s="2">
@@ -38444,7 +38444,7 @@
         <v>80</v>
       </c>
       <c r="AF269" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG269" t="s" s="2">
         <v>92</v>
@@ -38511,13 +38511,13 @@
         <v>80</v>
       </c>
       <c r="K270" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="L270" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M270" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="N270" s="2"/>
       <c r="O270" s="2"/>
@@ -38568,7 +38568,7 @@
         <v>80</v>
       </c>
       <c r="AF270" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AG270" t="s" s="2">
         <v>81</v>
@@ -39141,7 +39141,7 @@
         <v>93</v>
       </c>
       <c r="K275" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="L275" t="s" s="2">
         <v>930</v>
@@ -40020,13 +40020,13 @@
         <v>137</v>
       </c>
       <c r="L282" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="M282" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N282" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O282" s="2"/>
       <c r="P282" t="s" s="2">
@@ -40076,7 +40076,7 @@
         <v>80</v>
       </c>
       <c r="AF282" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG282" t="s" s="2">
         <v>92</v>
@@ -40146,10 +40146,10 @@
         <v>154</v>
       </c>
       <c r="L283" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M283" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="N283" s="2"/>
       <c r="O283" s="2"/>
@@ -40198,7 +40198,7 @@
         <v>80</v>
       </c>
       <c r="AF283" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AG283" t="s" s="2">
         <v>81</v>
@@ -40502,7 +40502,7 @@
       </c>
       <c r="E286" s="2"/>
       <c r="F286" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="G286" t="s" s="2">
         <v>82</v>
@@ -41020,13 +41020,13 @@
         <v>137</v>
       </c>
       <c r="L290" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="M290" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N290" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O290" s="2"/>
       <c r="P290" t="s" s="2">
@@ -41076,7 +41076,7 @@
         <v>80</v>
       </c>
       <c r="AF290" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG290" t="s" s="2">
         <v>92</v>
@@ -41146,10 +41146,10 @@
         <v>1058</v>
       </c>
       <c r="L291" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M291" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="N291" s="2"/>
       <c r="O291" s="2"/>
@@ -41200,7 +41200,7 @@
         <v>80</v>
       </c>
       <c r="AF291" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AG291" t="s" s="2">
         <v>81</v>
@@ -41644,13 +41644,13 @@
         <v>137</v>
       </c>
       <c r="L295" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="M295" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N295" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O295" s="2"/>
       <c r="P295" t="s" s="2">
@@ -41700,7 +41700,7 @@
         <v>80</v>
       </c>
       <c r="AF295" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG295" t="s" s="2">
         <v>92</v>
@@ -41770,10 +41770,10 @@
         <v>1058</v>
       </c>
       <c r="L296" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M296" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="N296" s="2"/>
       <c r="O296" s="2"/>
@@ -41824,7 +41824,7 @@
         <v>80</v>
       </c>
       <c r="AF296" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AG296" t="s" s="2">
         <v>81</v>
@@ -42020,13 +42020,13 @@
         <v>137</v>
       </c>
       <c r="L298" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="M298" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N298" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O298" s="2"/>
       <c r="P298" t="s" s="2">
@@ -42076,7 +42076,7 @@
         <v>80</v>
       </c>
       <c r="AF298" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG298" t="s" s="2">
         <v>92</v>
@@ -42143,13 +42143,13 @@
         <v>80</v>
       </c>
       <c r="K299" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="L299" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M299" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="N299" s="2"/>
       <c r="O299" s="2"/>
@@ -42200,7 +42200,7 @@
         <v>80</v>
       </c>
       <c r="AF299" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AG299" t="s" s="2">
         <v>81</v>
@@ -43774,13 +43774,13 @@
         <v>137</v>
       </c>
       <c r="L312" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="M312" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N312" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O312" s="2"/>
       <c r="P312" t="s" s="2">
@@ -43830,7 +43830,7 @@
         <v>80</v>
       </c>
       <c r="AF312" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG312" t="s" s="2">
         <v>92</v>
@@ -43900,10 +43900,10 @@
         <v>108</v>
       </c>
       <c r="L313" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M313" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="N313" s="2"/>
       <c r="O313" s="2"/>
@@ -43954,7 +43954,7 @@
         <v>80</v>
       </c>
       <c r="AF313" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AG313" t="s" s="2">
         <v>81</v>
@@ -44398,13 +44398,13 @@
         <v>137</v>
       </c>
       <c r="L317" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="M317" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N317" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O317" s="2"/>
       <c r="P317" t="s" s="2">
@@ -44454,7 +44454,7 @@
         <v>80</v>
       </c>
       <c r="AF317" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG317" t="s" s="2">
         <v>92</v>
@@ -44524,10 +44524,10 @@
         <v>108</v>
       </c>
       <c r="L318" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M318" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="N318" s="2"/>
       <c r="O318" s="2"/>
@@ -44576,7 +44576,7 @@
         <v>80</v>
       </c>
       <c r="AF318" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AG318" t="s" s="2">
         <v>81</v>
@@ -45146,13 +45146,13 @@
         <v>137</v>
       </c>
       <c r="L323" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="M323" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N323" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O323" s="2"/>
       <c r="P323" t="s" s="2">
@@ -45202,7 +45202,7 @@
         <v>80</v>
       </c>
       <c r="AF323" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG323" t="s" s="2">
         <v>92</v>
@@ -45272,10 +45272,10 @@
         <v>108</v>
       </c>
       <c r="L324" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M324" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="N324" s="2"/>
       <c r="O324" s="2"/>
@@ -45326,7 +45326,7 @@
         <v>80</v>
       </c>
       <c r="AF324" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AG324" t="s" s="2">
         <v>81</v>
@@ -45770,13 +45770,13 @@
         <v>137</v>
       </c>
       <c r="L328" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="M328" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N328" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O328" s="2"/>
       <c r="P328" t="s" s="2">
@@ -45826,7 +45826,7 @@
         <v>80</v>
       </c>
       <c r="AF328" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG328" t="s" s="2">
         <v>92</v>
@@ -45896,10 +45896,10 @@
         <v>108</v>
       </c>
       <c r="L329" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M329" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="N329" s="2"/>
       <c r="O329" s="2"/>
@@ -45950,7 +45950,7 @@
         <v>80</v>
       </c>
       <c r="AF329" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AG329" t="s" s="2">
         <v>81</v>
@@ -46394,13 +46394,13 @@
         <v>137</v>
       </c>
       <c r="L333" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="M333" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N333" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O333" s="2"/>
       <c r="P333" t="s" s="2">
@@ -46450,7 +46450,7 @@
         <v>80</v>
       </c>
       <c r="AF333" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG333" t="s" s="2">
         <v>92</v>
@@ -46520,10 +46520,10 @@
         <v>108</v>
       </c>
       <c r="L334" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M334" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="N334" s="2"/>
       <c r="O334" s="2"/>
@@ -46574,7 +46574,7 @@
         <v>80</v>
       </c>
       <c r="AF334" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AG334" t="s" s="2">
         <v>81</v>
@@ -47385,7 +47385,7 @@
         <v>93</v>
       </c>
       <c r="K341" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="L341" t="s" s="2">
         <v>1246</v>
@@ -49269,7 +49269,7 @@
         <v>80</v>
       </c>
       <c r="K356" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L356" t="s" s="2">
         <v>1314</v>
@@ -49754,7 +49754,7 @@
       </c>
       <c r="E360" s="2"/>
       <c r="F360" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="G360" t="s" s="2">
         <v>82</v>
@@ -50903,7 +50903,7 @@
         <v>93</v>
       </c>
       <c r="K369" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="L369" t="s" s="2">
         <v>930</v>
